--- a/src/main/java/video/call/data/answers.xlsx
+++ b/src/main/java/video/call/data/answers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gen.data.test\src\main\java\video\call\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A99C5A-6112-498E-B380-DB6AFB932BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB11A3E-74DE-4719-9B95-F318D2D8A338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="My new backpack!" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5292" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4611" uniqueCount="874">
   <si>
     <t>Part</t>
   </si>
@@ -2287,51 +2287,12 @@
     <t>in_correct</t>
   </si>
   <si>
-    <t>back/pack/school</t>
-  </si>
-  <si>
-    <t>color/f/nine</t>
-  </si>
-  <si>
-    <t>red/pink</t>
-  </si>
-  <si>
-    <t>color/t</t>
-  </si>
-  <si>
-    <t>yellow/blue</t>
-  </si>
-  <si>
     <t>e</t>
   </si>
   <si>
     <t>r</t>
   </si>
   <si>
-    <t>they're/t</t>
-  </si>
-  <si>
-    <t>I/have/hands</t>
-  </si>
-  <si>
-    <t>one/hand</t>
-  </si>
-  <si>
-    <t>I/can/draw/is/easy/drawing</t>
-  </si>
-  <si>
-    <t>I'm/thirsty/have/to/drink/okay</t>
-  </si>
-  <si>
-    <t>thanks/please/bad</t>
-  </si>
-  <si>
-    <t>juice/coke</t>
-  </si>
-  <si>
-    <t>wine/beer/alcohol/drug</t>
-  </si>
-  <si>
     <t>apple</t>
   </si>
   <si>
@@ -2344,60 +2305,15 @@
     <t>black</t>
   </si>
   <si>
-    <t>Yes/Yes, I have a backpack.</t>
-  </si>
-  <si>
-    <t>No/No, I don't have a backpack/don't</t>
-  </si>
-  <si>
-    <t>have/a/backpack/I</t>
-  </si>
-  <si>
     <t>They're hands.</t>
   </si>
   <si>
-    <t xml:space="preserve"> 2 hands/ I have 2 hands/two</t>
-  </si>
-  <si>
-    <t>3 hand/three</t>
-  </si>
-  <si>
-    <t>0 hand/1hand/one/zero</t>
-  </si>
-  <si>
     <t>small/ tiny</t>
   </si>
   <si>
     <t>big/ huge</t>
   </si>
   <si>
-    <t>yes/Yes, I can draw/ Drawing is easy</t>
-  </si>
-  <si>
-    <t>no/No, I can't draw./ Drawing is hard.</t>
-  </si>
-  <si>
-    <t>yes/Yes, I'm thirsty./ I have to drink</t>
-  </si>
-  <si>
-    <t>no/No, I'm not thirsty./ I'm okay</t>
-  </si>
-  <si>
-    <t>Yes/Yes,thanks/milk/Yes, please</t>
-  </si>
-  <si>
-    <t>No/Milk is bad</t>
-  </si>
-  <si>
-    <t>Yes, I like milk/ I love it/yes</t>
-  </si>
-  <si>
-    <t>No, I don't like milk/ Milk is bad/No</t>
-  </si>
-  <si>
-    <t>I/like/milk/love/it/is/bad</t>
-  </si>
-  <si>
     <t>orange</t>
   </si>
   <si>
@@ -2437,30 +2353,12 @@
     <t>green</t>
   </si>
   <si>
-    <t>green beans/ onion/ both/beans</t>
-  </si>
-  <si>
     <t>Yes/ Yes, I want corn</t>
   </si>
   <si>
-    <t>No/No, I don't want corn</t>
-  </si>
-  <si>
-    <t>corn/want/i</t>
-  </si>
-  <si>
-    <t>Beansprouts/Bamboo Shoot</t>
-  </si>
-  <si>
     <t>Yes/ Yeah/ Yep</t>
   </si>
   <si>
-    <t>rice/egg</t>
-  </si>
-  <si>
-    <t>no/nothing</t>
-  </si>
-  <si>
     <t>else</t>
   </si>
   <si>
@@ -2473,66 +2371,21 @@
     <t>awesome/ great/ not too bad</t>
   </si>
   <si>
-    <t>yes/Yes, I like swimming</t>
-  </si>
-  <si>
-    <t>I/like</t>
-  </si>
-  <si>
-    <t>no/No, I don't like swimming/don't</t>
-  </si>
-  <si>
-    <t>camping/swimming</t>
-  </si>
-  <si>
     <t>snowball fight</t>
   </si>
   <si>
     <t>gang violence</t>
   </si>
   <si>
-    <t>violence/fight</t>
-  </si>
-  <si>
-    <t>Yes, I want to join./ Sounds fun/yes</t>
-  </si>
-  <si>
-    <t>Sorry/ No, I don't./ I'm busy/don't</t>
-  </si>
-  <si>
-    <t>sound/r</t>
-  </si>
-  <si>
-    <t>grapes/orange/pineapple</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Yes, I like fruits/yes</t>
-  </si>
-  <si>
-    <t>No, I don't like fruits/no/don't</t>
-  </si>
-  <si>
-    <t>i/like/fruits</t>
-  </si>
-  <si>
     <t>grapes/ oranges/ pineapples</t>
   </si>
   <si>
-    <t>Yes, I do/yes</t>
-  </si>
-  <si>
-    <t>No, I don't/no/don't</t>
-  </si>
-  <si>
     <t>orange juice</t>
   </si>
   <si>
     <t>It's a sunflower</t>
   </si>
   <si>
-    <t>a/it</t>
-  </si>
-  <si>
     <t>yellow/ brown/ orange/ green</t>
   </si>
   <si>
@@ -2566,9 +2419,6 @@
     <t>It's an airplane</t>
   </si>
   <si>
-    <t>it/an/air</t>
-  </si>
-  <si>
     <t>a bike/ bicycle</t>
   </si>
   <si>
@@ -2578,9 +2428,6 @@
     <t>a bike</t>
   </si>
   <si>
-    <t>an/e</t>
-  </si>
-  <si>
     <t>the airplane</t>
   </si>
   <si>
@@ -2593,9 +2440,6 @@
     <t>train</t>
   </si>
   <si>
-    <t>too big/huge</t>
-  </si>
-  <si>
     <t>Fine/ It fits her</t>
   </si>
   <si>
@@ -2605,9 +2449,6 @@
     <t>purple</t>
   </si>
   <si>
-    <t>too small/tight/tiny</t>
-  </si>
-  <si>
     <t>white</t>
   </si>
   <si>
@@ -2617,43 +2458,202 @@
     <t>red</t>
   </si>
   <si>
-    <t>nine/t</t>
-  </si>
-  <si>
-    <t>Yes, it fits her/ She'll like it/yes</t>
-  </si>
-  <si>
-    <t>No, it doesn't fit her/no</t>
-  </si>
-  <si>
     <t>It's a rug</t>
   </si>
   <si>
     <t>It's a chair</t>
   </si>
   <si>
-    <t>It/a</t>
-  </si>
-  <si>
     <t>a plant</t>
   </si>
   <si>
-    <t>television/sofa</t>
-  </si>
-  <si>
     <t>plant</t>
   </si>
   <si>
-    <t>too/it/f</t>
-  </si>
-  <si>
-    <t>it/get</t>
-  </si>
-  <si>
-    <t>aw/too/not</t>
-  </si>
-  <si>
-    <t>no,ran</t>
+    <t>yes/ Yes, I'm thirsty./ I have to drink</t>
+  </si>
+  <si>
+    <t>no/ No, I'm not thirsty./ I'm okay</t>
+  </si>
+  <si>
+    <t>Yes/ Yes,thanks/ milk/ Yes, please</t>
+  </si>
+  <si>
+    <t>No/ Milk is bad</t>
+  </si>
+  <si>
+    <t>yes/ Yes, I can draw/ Drawing is easy</t>
+  </si>
+  <si>
+    <t>no/ No, I can't draw./ Drawing is hard.</t>
+  </si>
+  <si>
+    <t>back/ pack/ school</t>
+  </si>
+  <si>
+    <t>color/ f/ nine</t>
+  </si>
+  <si>
+    <t>Yes/ Yes, I have a backpack.</t>
+  </si>
+  <si>
+    <t>No/ No, I don't have a backpack/ don't</t>
+  </si>
+  <si>
+    <t>have/ a/ backpack/ I</t>
+  </si>
+  <si>
+    <t>red/ pink</t>
+  </si>
+  <si>
+    <t>color/ t</t>
+  </si>
+  <si>
+    <t>yellow/ blue</t>
+  </si>
+  <si>
+    <t>they're/ t</t>
+  </si>
+  <si>
+    <t>3 hand/ three</t>
+  </si>
+  <si>
+    <t>0 hand/ 1hand/ one/ zero</t>
+  </si>
+  <si>
+    <t>I/ have/ hands</t>
+  </si>
+  <si>
+    <t>one/ hand</t>
+  </si>
+  <si>
+    <t>I/ can/ draw/ is/ easy/ drawing</t>
+  </si>
+  <si>
+    <t>thanks/ please/ bad</t>
+  </si>
+  <si>
+    <t>I/ like/ milk/ love/ it/ is/ bad</t>
+  </si>
+  <si>
+    <t>juice/ coke</t>
+  </si>
+  <si>
+    <t>wine/ beer/ alcohol/ drug</t>
+  </si>
+  <si>
+    <t>no/ ran</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2 hands/ I have 2 hands/ two</t>
+  </si>
+  <si>
+    <t>Yes, I like milk/ I love it/ yes</t>
+  </si>
+  <si>
+    <t>No, I don't like milk/ Milk is bad/ No</t>
+  </si>
+  <si>
+    <t>No/ No, I don't want corn</t>
+  </si>
+  <si>
+    <t>corn/ want/ i</t>
+  </si>
+  <si>
+    <t>Beansprouts/ Bamboo Shoot</t>
+  </si>
+  <si>
+    <t>rice/ egg</t>
+  </si>
+  <si>
+    <t>no/ nothing</t>
+  </si>
+  <si>
+    <t>green beans/ onion/ both/ beans</t>
+  </si>
+  <si>
+    <t>aw/ too/ not</t>
+  </si>
+  <si>
+    <t>yes/ Yes, I like swimming</t>
+  </si>
+  <si>
+    <t>no/ No, I don't like swimming/ don't</t>
+  </si>
+  <si>
+    <t>I/ like</t>
+  </si>
+  <si>
+    <t>camping/ swimming</t>
+  </si>
+  <si>
+    <t>violence/ fight</t>
+  </si>
+  <si>
+    <t>sound/ r</t>
+  </si>
+  <si>
+    <t>Yes, I want to join./ Sounds fun/ yes</t>
+  </si>
+  <si>
+    <t>Sorry/ No, I don't./ I'm busy/ don't</t>
+  </si>
+  <si>
+    <t>grapes/ orange/ pineapple</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yes, I like fruits/ yes</t>
+  </si>
+  <si>
+    <t>No, I don't like fruits/ no/ don't</t>
+  </si>
+  <si>
+    <t>i/ like/ fruits</t>
+  </si>
+  <si>
+    <t>Yes, I do/ yes</t>
+  </si>
+  <si>
+    <t>No, I don't/ no/ don't</t>
+  </si>
+  <si>
+    <t>a/ it</t>
+  </si>
+  <si>
+    <t>it/ an/ air</t>
+  </si>
+  <si>
+    <t>an/ e</t>
+  </si>
+  <si>
+    <t>it/ get</t>
+  </si>
+  <si>
+    <t>too big/ huge</t>
+  </si>
+  <si>
+    <t>too small/ tight/ tiny</t>
+  </si>
+  <si>
+    <t>too/ it/ f</t>
+  </si>
+  <si>
+    <t>nine/ t</t>
+  </si>
+  <si>
+    <t>No, it doesn't fit her/ no</t>
+  </si>
+  <si>
+    <t>Yes, it fits her/ She'll like it/ yes</t>
+  </si>
+  <si>
+    <t>It/ a</t>
+  </si>
+  <si>
+    <t>television/ sofa</t>
+  </si>
+  <si>
+    <t>I'm/ thirsty/ have/ to/ drink</t>
   </si>
 </sst>
 </file>
@@ -3141,7 +3141,7 @@
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3289,7 +3289,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>751</v>
+        <v>818</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -3405,7 +3405,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>752</v>
+        <v>819</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -3669,7 +3669,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>770</v>
+        <v>820</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -3698,7 +3698,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>771</v>
+        <v>821</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -3846,7 +3846,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>772</v>
+        <v>822</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>753</v>
+        <v>823</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -4110,7 +4110,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="s">
-        <v>754</v>
+        <v>824</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -4176,7 +4176,7 @@
         <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>809</v>
+        <v>775</v>
       </c>
       <c r="C40" t="s">
         <v>139</v>
@@ -4226,7 +4226,7 @@
         <v>7</v>
       </c>
       <c r="I41" t="s">
-        <v>755</v>
+        <v>825</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -4374,7 +4374,7 @@
         <v>7</v>
       </c>
       <c r="J46" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -4596,7 +4596,7 @@
         <v>607</v>
       </c>
       <c r="I4" t="s">
-        <v>843</v>
+        <v>794</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4744,7 +4744,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>844</v>
+        <v>862</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -4860,7 +4860,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>845</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -5008,7 +5008,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>810</v>
+        <v>776</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -5124,7 +5124,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>846</v>
+        <v>796</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -5153,7 +5153,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>847</v>
+        <v>797</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -5301,7 +5301,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -5417,7 +5417,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>849</v>
+        <v>798</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -5446,7 +5446,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>850</v>
+        <v>799</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -5475,7 +5475,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>851</v>
+        <v>800</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -5504,7 +5504,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>852</v>
+        <v>801</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -5649,7 +5649,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -5870,7 +5870,7 @@
         <v>660</v>
       </c>
       <c r="I4" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5899,7 +5899,7 @@
         <v>663</v>
       </c>
       <c r="I5" t="s">
-        <v>857</v>
+        <v>866</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -5928,7 +5928,7 @@
         <v>665</v>
       </c>
       <c r="I6" t="s">
-        <v>854</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -5957,7 +5957,7 @@
         <v>666</v>
       </c>
       <c r="I7" t="s">
-        <v>855</v>
+        <v>803</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -6099,7 +6099,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -6215,7 +6215,7 @@
         <v>7</v>
       </c>
       <c r="I16" t="s">
-        <v>856</v>
+        <v>804</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -6244,7 +6244,7 @@
         <v>7</v>
       </c>
       <c r="I17" t="s">
-        <v>858</v>
+        <v>805</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -6273,7 +6273,7 @@
         <v>7</v>
       </c>
       <c r="I18" t="s">
-        <v>859</v>
+        <v>806</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -6302,7 +6302,7 @@
         <v>7</v>
       </c>
       <c r="I19" t="s">
-        <v>860</v>
+        <v>807</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6479,7 +6479,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="I29" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -6624,7 +6624,7 @@
         <v>7</v>
       </c>
       <c r="I30" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -6772,7 +6772,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -6992,7 +6992,7 @@
         <v>708</v>
       </c>
       <c r="I4" t="s">
-        <v>864</v>
+        <v>808</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -7140,7 +7140,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -7253,7 +7253,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>865</v>
+        <v>809</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -7401,7 +7401,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -7517,7 +7517,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>867</v>
+        <v>810</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -7665,7 +7665,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -7781,7 +7781,7 @@
         <v>7</v>
       </c>
       <c r="I31" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -7810,7 +7810,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>869</v>
+        <v>811</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -7839,7 +7839,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>797</v>
+        <v>769</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -8205,7 +8205,7 @@
         <v>168</v>
       </c>
       <c r="I4" t="s">
-        <v>773</v>
+        <v>757</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -8353,7 +8353,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>758</v>
+        <v>826</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -8469,7 +8469,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>774</v>
+        <v>837</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -8498,7 +8498,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>775</v>
+        <v>827</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -8527,7 +8527,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>776</v>
+        <v>828</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -8663,7 +8663,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>759</v>
+        <v>829</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -8767,7 +8767,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -8793,7 +8793,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>778</v>
+        <v>759</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>760</v>
+        <v>830</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -9057,7 +9057,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>779</v>
+        <v>816</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -9086,7 +9086,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>780</v>
+        <v>817</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -9234,7 +9234,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>761</v>
+        <v>831</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -9560,7 +9560,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="s">
-        <v>781</v>
+        <v>812</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -9586,7 +9586,7 @@
         <v>7</v>
       </c>
       <c r="I5" t="s">
-        <v>782</v>
+        <v>813</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -9719,7 +9719,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>762</v>
+        <v>873</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -9823,7 +9823,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>783</v>
+        <v>814</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -9849,7 +9849,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>784</v>
+        <v>815</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -9982,7 +9982,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>763</v>
+        <v>832</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -10086,7 +10086,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>785</v>
+        <v>838</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -10112,7 +10112,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>786</v>
+        <v>839</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -10245,7 +10245,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>787</v>
+        <v>833</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -10349,7 +10349,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>764</v>
+        <v>834</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -10375,7 +10375,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>765</v>
+        <v>835</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -10401,7 +10401,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -10534,7 +10534,7 @@
         <v>7</v>
       </c>
       <c r="J41" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -10875,7 +10875,7 @@
         <v>287</v>
       </c>
       <c r="I4" t="s">
-        <v>788</v>
+        <v>760</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -11020,7 +11020,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>789</v>
+        <v>761</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -11165,7 +11165,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>792</v>
+        <v>764</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -11342,7 +11342,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>795</v>
+        <v>767</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -11455,7 +11455,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>792</v>
+        <v>764</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -11484,7 +11484,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>793</v>
+        <v>765</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -11513,7 +11513,7 @@
         <v>7</v>
       </c>
       <c r="I26" t="s">
-        <v>796</v>
+        <v>768</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="s">
-        <v>873</v>
+        <v>836</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -11777,7 +11777,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -11806,7 +11806,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>797</v>
+        <v>769</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -11954,7 +11954,7 @@
         <v>7</v>
       </c>
       <c r="J41" t="s">
-        <v>798</v>
+        <v>770</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -12196,7 +12196,7 @@
         <v>343</v>
       </c>
       <c r="I4" t="s">
-        <v>801</v>
+        <v>845</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -12225,7 +12225,7 @@
         <v>346</v>
       </c>
       <c r="I5" t="s">
-        <v>799</v>
+        <v>771</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -12373,7 +12373,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>800</v>
+        <v>772</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -12489,7 +12489,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>802</v>
+        <v>773</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -12518,7 +12518,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>803</v>
+        <v>840</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -12666,7 +12666,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>804</v>
+        <v>841</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -12782,7 +12782,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>805</v>
+        <v>842</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -12811,7 +12811,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>797</v>
+        <v>769</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -12959,7 +12959,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -13075,7 +13075,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -13104,7 +13104,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>807</v>
+        <v>843</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -13133,7 +13133,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>808</v>
+        <v>844</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -13281,7 +13281,7 @@
         <v>7</v>
       </c>
       <c r="J41" t="s">
-        <v>810</v>
+        <v>776</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -13502,7 +13502,7 @@
         <v>401</v>
       </c>
       <c r="I4" t="s">
-        <v>811</v>
+        <v>777</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -13531,7 +13531,7 @@
         <v>404</v>
       </c>
       <c r="I5" t="s">
-        <v>812</v>
+        <v>778</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -13679,7 +13679,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>872</v>
+        <v>846</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -13795,7 +13795,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>813</v>
+        <v>847</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -13824,7 +13824,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>815</v>
+        <v>848</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -13972,7 +13972,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>814</v>
+        <v>849</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -14088,7 +14088,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>816</v>
+        <v>850</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -14117,7 +14117,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>817</v>
+        <v>779</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -14146,7 +14146,7 @@
         <v>7</v>
       </c>
       <c r="I26" t="s">
-        <v>794</v>
+        <v>766</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -14175,7 +14175,7 @@
         <v>7</v>
       </c>
       <c r="I27" t="s">
-        <v>818</v>
+        <v>780</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -14323,7 +14323,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="s">
-        <v>819</v>
+        <v>851</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -14439,7 +14439,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>820</v>
+        <v>853</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -14468,7 +14468,7 @@
         <v>7</v>
       </c>
       <c r="I37" t="s">
-        <v>821</v>
+        <v>854</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -14616,7 +14616,7 @@
         <v>7</v>
       </c>
       <c r="J42" t="s">
-        <v>822</v>
+        <v>852</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -14836,7 +14836,7 @@
         <v>327</v>
       </c>
       <c r="I4" t="s">
-        <v>823</v>
+        <v>855</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -14984,7 +14984,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>790</v>
+        <v>762</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -15088,7 +15088,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>824</v>
+        <v>856</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -15111,7 +15111,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>825</v>
+        <v>857</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -15229,7 +15229,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="s">
-        <v>826</v>
+        <v>858</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -15333,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>827</v>
+        <v>781</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -15362,7 +15362,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>797</v>
+        <v>769</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -15510,7 +15510,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="s">
-        <v>791</v>
+        <v>763</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -15626,7 +15626,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>828</v>
+        <v>859</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -15655,7 +15655,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -15684,7 +15684,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>830</v>
+        <v>782</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -15832,7 +15832,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>795</v>
+        <v>767</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -16041,7 +16041,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="s">
-        <v>831</v>
+        <v>783</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -16144,7 +16144,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>832</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -16227,7 +16227,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>833</v>
+        <v>784</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -16330,7 +16330,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -16413,7 +16413,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>778</v>
+        <v>759</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -16436,7 +16436,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -16539,7 +16539,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>795</v>
+        <v>767</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -16622,7 +16622,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>834</v>
+        <v>785</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -16645,7 +16645,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>835</v>
+        <v>786</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -16748,7 +16748,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -16942,7 +16942,7 @@
         <v>556</v>
       </c>
       <c r="I4" t="s">
-        <v>836</v>
+        <v>787</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -16971,7 +16971,7 @@
         <v>559</v>
       </c>
       <c r="I5" t="s">
-        <v>837</v>
+        <v>788</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -17116,7 +17116,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -17232,7 +17232,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>838</v>
+        <v>789</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -17261,7 +17261,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>839</v>
+        <v>790</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -17409,7 +17409,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>795</v>
+        <v>767</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -17525,7 +17525,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>840</v>
+        <v>791</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -17554,7 +17554,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>841</v>
+        <v>792</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -17583,7 +17583,7 @@
         <v>7</v>
       </c>
       <c r="I26" t="s">
-        <v>797</v>
+        <v>769</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -17702,7 +17702,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>810</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -17847,7 +17847,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>842</v>
+        <v>793</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -17995,7 +17995,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>791</v>
+        <v>763</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">

--- a/src/main/java/video/call/data/answers.xlsx
+++ b/src/main/java/video/call/data/answers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gen.data.test\src\main\java\video\call\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB11A3E-74DE-4719-9B95-F318D2D8A338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEACF330-BD37-40E2-AC3F-05BD6DBA8DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="My new backpack!" sheetId="1" r:id="rId1"/>
@@ -2482,9 +2482,6 @@
     <t>No/ Milk is bad</t>
   </si>
   <si>
-    <t>yes/ Yes, I can draw/ Drawing is easy</t>
-  </si>
-  <si>
     <t>no/ No, I can't draw./ Drawing is hard.</t>
   </si>
   <si>
@@ -2527,15 +2524,9 @@
     <t>one/ hand</t>
   </si>
   <si>
-    <t>I/ can/ draw/ is/ easy/ drawing</t>
-  </si>
-  <si>
     <t>thanks/ please/ bad</t>
   </si>
   <si>
-    <t>I/ like/ milk/ love/ it/ is/ bad</t>
-  </si>
-  <si>
     <t>juice/ coke</t>
   </si>
   <si>
@@ -2548,9 +2539,6 @@
     <t xml:space="preserve"> 2 hands/ I have 2 hands/ two</t>
   </si>
   <si>
-    <t>Yes, I like milk/ I love it/ yes</t>
-  </si>
-  <si>
     <t>No, I don't like milk/ Milk is bad/ No</t>
   </si>
   <si>
@@ -2654,6 +2642,18 @@
   </si>
   <si>
     <t>I'm/ thirsty/ have/ to/ drink</t>
+  </si>
+  <si>
+    <t>yes/ Yes, I can draw/ Drawing is easy/ easy</t>
+  </si>
+  <si>
+    <t>I/ can/ draw/ is/ drawing</t>
+  </si>
+  <si>
+    <t>I/ like/ milk/ it/ is/ bad</t>
+  </si>
+  <si>
+    <t>Yes, I like milk/ I love it/ yes/ love</t>
   </si>
 </sst>
 </file>
@@ -3289,7 +3289,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3553,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -3669,7 +3669,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -3698,7 +3698,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -3846,7 +3846,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -4110,7 +4110,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -4226,7 +4226,7 @@
         <v>7</v>
       </c>
       <c r="I41" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -4744,7 +4744,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -5301,7 +5301,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -5649,7 +5649,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -5870,7 +5870,7 @@
         <v>660</v>
       </c>
       <c r="I4" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5899,7 +5899,7 @@
         <v>663</v>
       </c>
       <c r="I5" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -6099,7 +6099,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -6479,7 +6479,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -6595,7 +6595,7 @@
         <v>7</v>
       </c>
       <c r="I29" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -6624,7 +6624,7 @@
         <v>7</v>
       </c>
       <c r="I30" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -7140,7 +7140,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -7401,7 +7401,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -7665,7 +7665,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -7781,7 +7781,7 @@
         <v>7</v>
       </c>
       <c r="I31" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -8353,7 +8353,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -8469,7 +8469,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -8498,7 +8498,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -8527,7 +8527,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -8663,7 +8663,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -9057,7 +9057,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>816</v>
+        <v>870</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -9086,7 +9086,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -9234,7 +9234,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>831</v>
+        <v>871</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -9719,7 +9719,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -9982,7 +9982,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -10086,7 +10086,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>838</v>
+        <v>873</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -10112,7 +10112,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -10245,7 +10245,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>833</v>
+        <v>872</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -10349,7 +10349,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -10375,7 +10375,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -11661,7 +11661,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -12196,7 +12196,7 @@
         <v>343</v>
       </c>
       <c r="I4" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -12518,7 +12518,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -12666,7 +12666,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -12782,7 +12782,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -13104,7 +13104,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -13133,7 +13133,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -13679,7 +13679,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -13795,7 +13795,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -13824,7 +13824,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -13972,7 +13972,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -14088,7 +14088,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -14323,7 +14323,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -14439,7 +14439,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -14468,7 +14468,7 @@
         <v>7</v>
       </c>
       <c r="I37" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -14616,7 +14616,7 @@
         <v>7</v>
       </c>
       <c r="J42" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -14836,7 +14836,7 @@
         <v>327</v>
       </c>
       <c r="I4" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -15088,7 +15088,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -15111,7 +15111,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -15229,7 +15229,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -15626,7 +15626,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -15655,7 +15655,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -16144,7 +16144,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">

--- a/src/main/java/video/call/data/answers.xlsx
+++ b/src/main/java/video/call/data/answers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gen.data.test\src\main\java\video\call\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEACF330-BD37-40E2-AC3F-05BD6DBA8DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DD4D9A-4C03-4281-A708-E5D0756A470F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="My new backpack!" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4611" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4566" uniqueCount="878">
   <si>
     <t>Part</t>
   </si>
@@ -1990,9 +1990,6 @@
   </si>
   <si>
     <t>We had so much fun talking about transportation. I'll see you in the next lesson. Bye bye!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hi, Amy's birthday is coming soon. Let's get her some new items of clothes. </t>
   </si>
   <si>
     <t>Jeans, pink dress, red dress, hat</t>
@@ -2654,13 +2651,28 @@
   </si>
   <si>
     <t>Yes, I like milk/ I love it/ yes/ love</t>
+  </si>
+  <si>
+    <t>Hi, Amy's birthday is coming soon. Let's get her some new items of clothes.</t>
+  </si>
+  <si>
+    <t>1_11</t>
+  </si>
+  <si>
+    <t>1_12</t>
+  </si>
+  <si>
+    <t>2_12</t>
+  </si>
+  <si>
+    <t>2_13</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -2674,16 +2686,62 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2691,14 +2749,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3051,10 +3148,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -3141,7 +3238,7 @@
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3289,7 +3386,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -3405,7 +3502,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -3553,7 +3650,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -3669,7 +3766,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -3698,7 +3795,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -3846,7 +3943,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -3962,7 +4059,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -4110,7 +4207,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -4176,7 +4273,7 @@
         <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C40" t="s">
         <v>139</v>
@@ -4226,7 +4323,7 @@
         <v>7</v>
       </c>
       <c r="I41" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -4374,7 +4471,7 @@
         <v>7</v>
       </c>
       <c r="J46" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -4506,10 +4603,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -4596,7 +4693,7 @@
         <v>607</v>
       </c>
       <c r="I4" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4744,7 +4841,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -4860,7 +4957,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -5008,7 +5105,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -5124,7 +5221,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -5153,7 +5250,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -5301,7 +5398,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -5417,7 +5514,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -5446,7 +5543,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -5475,7 +5572,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -5504,7 +5601,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -5649,7 +5746,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -5754,7 +5851,7 @@
     <col min="9" max="10" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5780,1075 +5877,1005 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
       </c>
-      <c r="J1" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
         <v>653</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>654</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="6" t="s">
         <v>655</v>
       </c>
-      <c r="I2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
         <v>656</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="I3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
         <v>659</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="I4" t="s">
+      <c r="C5" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>662</v>
+      </c>
+      <c r="I5" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="C5" t="s">
-        <v>662</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" t="s">
-        <v>663</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>664</v>
+      </c>
+      <c r="I6" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>665</v>
+      </c>
+      <c r="I7" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" t="s">
+        <v>667</v>
+      </c>
+      <c r="I8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" t="s">
+        <v>7</v>
+      </c>
+      <c r="J12" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>664</v>
-      </c>
-      <c r="C6" t="s">
-        <v>662</v>
-      </c>
-      <c r="D6" t="s">
+    <row r="13" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" t="s">
-        <v>665</v>
-      </c>
-      <c r="I6" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>288</v>
-      </c>
-      <c r="C7" t="s">
-        <v>662</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" t="s">
-        <v>666</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="E13" s="5"/>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="17" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" t="s">
+        <v>7</v>
+      </c>
+      <c r="I20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C8" t="s">
-        <v>667</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" t="s">
-        <v>668</v>
-      </c>
-      <c r="I8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>669</v>
-      </c>
-      <c r="C9" t="s">
-        <v>662</v>
-      </c>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C21" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>670</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C23" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" t="s">
-        <v>671</v>
-      </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C24" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C12" t="s">
-        <v>672</v>
-      </c>
-      <c r="D12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H12" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" t="s">
-        <v>7</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="C25" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" t="s">
+        <v>7</v>
+      </c>
+      <c r="J25" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="26" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C13" t="s">
-        <v>662</v>
-      </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" t="s">
-        <v>7</v>
-      </c>
-      <c r="I13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C26" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" t="s">
-        <v>7</v>
-      </c>
-      <c r="H14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>525</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" t="s">
-        <v>673</v>
-      </c>
-      <c r="D15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H15" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" t="s">
-        <v>674</v>
-      </c>
-      <c r="C16" t="s">
-        <v>675</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" t="s">
-        <v>7</v>
-      </c>
-      <c r="H16" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" t="s">
-        <v>676</v>
-      </c>
-      <c r="C17" t="s">
-        <v>677</v>
-      </c>
-      <c r="D17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" t="s">
-        <v>7</v>
-      </c>
-      <c r="H17" t="s">
-        <v>7</v>
-      </c>
-      <c r="I17" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" t="s">
-        <v>678</v>
-      </c>
-      <c r="C18" t="s">
-        <v>679</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18" t="s">
-        <v>7</v>
-      </c>
-      <c r="H18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C19" t="s">
-        <v>681</v>
-      </c>
-      <c r="D19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19" t="s">
-        <v>7</v>
-      </c>
-      <c r="H19" t="s">
-        <v>7</v>
-      </c>
-      <c r="I19" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" t="s">
-        <v>682</v>
-      </c>
-      <c r="C20" t="s">
-        <v>679</v>
-      </c>
-      <c r="D20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H20" t="s">
-        <v>7</v>
-      </c>
-      <c r="I20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" t="s">
-        <v>291</v>
-      </c>
-      <c r="C21" t="s">
-        <v>683</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" t="s">
-        <v>7</v>
-      </c>
-      <c r="H21" t="s">
-        <v>7</v>
-      </c>
-      <c r="I21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" t="s">
-        <v>684</v>
-      </c>
-      <c r="C22" t="s">
-        <v>685</v>
-      </c>
-      <c r="D22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" t="s">
-        <v>7</v>
-      </c>
-      <c r="H22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" t="s">
+        <v>7</v>
+      </c>
+      <c r="H27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" t="s">
+        <v>7</v>
+      </c>
+      <c r="I28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" t="s">
+        <v>7</v>
+      </c>
+      <c r="H32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C23" t="s">
-        <v>686</v>
-      </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23" t="s">
-        <v>7</v>
-      </c>
-      <c r="I23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C33" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" t="s">
+        <v>7</v>
+      </c>
+      <c r="H33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C24" t="s">
-        <v>687</v>
-      </c>
-      <c r="D24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" t="s">
-        <v>7</v>
-      </c>
-      <c r="H24" t="s">
-        <v>7</v>
-      </c>
-      <c r="I24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>194</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C34" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C25" t="s">
-        <v>683</v>
-      </c>
-      <c r="D25" t="s">
-        <v>196</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" t="s">
-        <v>7</v>
-      </c>
-      <c r="I25" t="s">
-        <v>7</v>
-      </c>
-      <c r="J25" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C35" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35" t="s">
+        <v>7</v>
+      </c>
+      <c r="I35" t="s">
+        <v>7</v>
+      </c>
+      <c r="J35" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C26" t="s">
-        <v>687</v>
-      </c>
-      <c r="D26" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" t="s">
-        <v>7</v>
-      </c>
-      <c r="H26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>197</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C36" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" t="s">
+        <v>7</v>
+      </c>
+      <c r="I36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" t="s">
-        <v>198</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" t="s">
-        <v>7</v>
-      </c>
-      <c r="H27" t="s">
-        <v>7</v>
-      </c>
-      <c r="I27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" t="s">
-        <v>688</v>
-      </c>
-      <c r="D28" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>7</v>
-      </c>
-      <c r="G28" t="s">
-        <v>7</v>
-      </c>
-      <c r="H28" t="s">
-        <v>7</v>
-      </c>
-      <c r="I28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" t="s">
-        <v>689</v>
-      </c>
-      <c r="C29" t="s">
-        <v>690</v>
-      </c>
-      <c r="D29" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" t="s">
-        <v>7</v>
-      </c>
-      <c r="H29" t="s">
-        <v>7</v>
-      </c>
-      <c r="I29" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" t="s">
-        <v>691</v>
-      </c>
-      <c r="C30" t="s">
-        <v>692</v>
-      </c>
-      <c r="D30" t="s">
-        <v>94</v>
-      </c>
-      <c r="E30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" t="s">
-        <v>7</v>
-      </c>
-      <c r="H30" t="s">
-        <v>7</v>
-      </c>
-      <c r="I30" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" t="s">
-        <v>693</v>
-      </c>
-      <c r="D31" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" t="s">
-        <v>7</v>
-      </c>
-      <c r="H31" t="s">
-        <v>7</v>
-      </c>
-      <c r="I31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32" t="s">
-        <v>694</v>
-      </c>
-      <c r="C32" t="s">
-        <v>695</v>
-      </c>
-      <c r="D32" t="s">
-        <v>101</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" t="s">
-        <v>7</v>
-      </c>
-      <c r="H32" t="s">
-        <v>7</v>
-      </c>
-      <c r="I32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>696</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>7</v>
-      </c>
-      <c r="G33" t="s">
-        <v>7</v>
-      </c>
-      <c r="H33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" t="s">
-        <v>697</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>7</v>
-      </c>
-      <c r="G34" t="s">
-        <v>7</v>
-      </c>
-      <c r="H34" t="s">
-        <v>7</v>
-      </c>
-      <c r="I34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="C37" s="2"/>
+      <c r="D37" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" t="s">
+        <v>7</v>
+      </c>
+      <c r="I37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="D35" t="s">
-        <v>110</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" t="s">
-        <v>7</v>
-      </c>
-      <c r="H35" t="s">
-        <v>7</v>
-      </c>
-      <c r="I35" t="s">
-        <v>7</v>
-      </c>
-      <c r="J35" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>111</v>
-      </c>
-      <c r="B36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" t="s">
-        <v>697</v>
-      </c>
-      <c r="D36" t="s">
-        <v>107</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>7</v>
-      </c>
-      <c r="G36" t="s">
-        <v>7</v>
-      </c>
-      <c r="H36" t="s">
-        <v>7</v>
-      </c>
-      <c r="I36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>114</v>
-      </c>
-      <c r="B37" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37" t="s">
-        <v>7</v>
-      </c>
-      <c r="H37" t="s">
-        <v>7</v>
-      </c>
-      <c r="I37" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>157</v>
-      </c>
-      <c r="B38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" t="s">
-        <v>699</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="D38" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
+      <c r="E38" s="5"/>
       <c r="F38" t="s">
         <v>7</v>
       </c>
@@ -6902,10 +6929,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -6916,7 +6943,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -6928,10 +6955,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s">
+        <v>700</v>
+      </c>
+      <c r="H2" t="s">
         <v>701</v>
-      </c>
-      <c r="H2" t="s">
-        <v>702</v>
       </c>
       <c r="I2" t="s">
         <v>7</v>
@@ -6945,7 +6972,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -6960,7 +6987,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="I3" t="s">
         <v>7</v>
@@ -6971,10 +6998,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
+        <v>704</v>
+      </c>
+      <c r="C4" t="s">
         <v>705</v>
-      </c>
-      <c r="C4" t="s">
-        <v>706</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
@@ -6983,16 +7010,16 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
         <v>707</v>
       </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
-        <v>708</v>
-      </c>
       <c r="I4" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -7003,7 +7030,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
@@ -7018,7 +7045,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="I5" t="s">
         <v>7</v>
@@ -7032,7 +7059,7 @@
         <v>511</v>
       </c>
       <c r="C6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -7047,7 +7074,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I6" t="s">
         <v>7</v>
@@ -7076,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I7" t="s">
         <v>7</v>
@@ -7090,7 +7117,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D8" t="s">
         <v>41</v>
@@ -7099,7 +7126,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G8" t="s">
         <v>7</v>
@@ -7119,7 +7146,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D9" t="s">
         <v>46</v>
@@ -7140,7 +7167,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -7151,7 +7178,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
@@ -7160,7 +7187,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G10" t="s">
         <v>7</v>
@@ -7209,7 +7236,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D12" t="s">
         <v>56</v>
@@ -7232,10 +7259,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s">
+        <v>716</v>
+      </c>
+      <c r="C13" t="s">
         <v>717</v>
-      </c>
-      <c r="C13" t="s">
-        <v>718</v>
       </c>
       <c r="D13" t="s">
         <v>60</v>
@@ -7253,7 +7280,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -7264,7 +7291,7 @@
         <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D14" t="s">
         <v>64</v>
@@ -7293,7 +7320,7 @@
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D15" t="s">
         <v>69</v>
@@ -7351,7 +7378,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D17" t="s">
         <v>75</v>
@@ -7380,7 +7407,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D18" t="s">
         <v>78</v>
@@ -7401,7 +7428,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -7412,7 +7439,7 @@
         <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D19" t="s">
         <v>81</v>
@@ -7470,7 +7497,7 @@
         <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D21" t="s">
         <v>86</v>
@@ -7496,10 +7523,10 @@
         <v>87</v>
       </c>
       <c r="B22" t="s">
+        <v>724</v>
+      </c>
+      <c r="C22" t="s">
         <v>725</v>
-      </c>
-      <c r="C22" t="s">
-        <v>726</v>
       </c>
       <c r="D22" t="s">
         <v>90</v>
@@ -7517,7 +7544,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -7528,7 +7555,7 @@
         <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D23" t="s">
         <v>94</v>
@@ -7554,10 +7581,10 @@
         <v>95</v>
       </c>
       <c r="B24" t="s">
+        <v>727</v>
+      </c>
+      <c r="C24" t="s">
         <v>728</v>
-      </c>
-      <c r="C24" t="s">
-        <v>729</v>
       </c>
       <c r="D24" t="s">
         <v>97</v>
@@ -7586,7 +7613,7 @@
         <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D25" t="s">
         <v>101</v>
@@ -7615,7 +7642,7 @@
         <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D26" t="s">
         <v>104</v>
@@ -7644,7 +7671,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D27" t="s">
         <v>107</v>
@@ -7665,7 +7692,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -7676,7 +7703,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D28" t="s">
         <v>110</v>
@@ -7734,7 +7761,7 @@
         <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D30" t="s">
         <v>118</v>
@@ -7743,7 +7770,7 @@
         <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G30" t="s">
         <v>7</v>
@@ -7760,10 +7787,10 @@
         <v>119</v>
       </c>
       <c r="B31" t="s">
+        <v>735</v>
+      </c>
+      <c r="C31" t="s">
         <v>736</v>
-      </c>
-      <c r="C31" t="s">
-        <v>737</v>
       </c>
       <c r="D31" t="s">
         <v>122</v>
@@ -7781,7 +7808,7 @@
         <v>7</v>
       </c>
       <c r="I31" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -7789,10 +7816,10 @@
         <v>123</v>
       </c>
       <c r="B32" t="s">
+        <v>737</v>
+      </c>
+      <c r="C32" t="s">
         <v>738</v>
-      </c>
-      <c r="C32" t="s">
-        <v>739</v>
       </c>
       <c r="D32" t="s">
         <v>125</v>
@@ -7810,7 +7837,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -7821,7 +7848,7 @@
         <v>314</v>
       </c>
       <c r="C33" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D33" t="s">
         <v>129</v>
@@ -7839,7 +7866,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -7850,7 +7877,7 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D34" t="s">
         <v>132</v>
@@ -7876,10 +7903,10 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
+        <v>741</v>
+      </c>
+      <c r="C35" t="s">
         <v>742</v>
-      </c>
-      <c r="C35" t="s">
-        <v>743</v>
       </c>
       <c r="D35" t="s">
         <v>135</v>
@@ -7908,7 +7935,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D36" t="s">
         <v>137</v>
@@ -7937,7 +7964,7 @@
         <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D37" t="s">
         <v>222</v>
@@ -7966,7 +7993,7 @@
         <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D38" t="s">
         <v>225</v>
@@ -7995,7 +8022,7 @@
         <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D39" t="s">
         <v>227</v>
@@ -8053,7 +8080,7 @@
         <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D41" t="s">
         <v>159</v>
@@ -8115,10 +8142,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -8205,7 +8232,7 @@
         <v>168</v>
       </c>
       <c r="I4" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -8353,7 +8380,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -8469,7 +8496,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -8498,7 +8525,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -8527,7 +8554,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -8663,7 +8690,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -8767,7 +8794,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -8793,7 +8820,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -8941,7 +8968,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -9057,7 +9084,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -9086,7 +9113,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -9234,7 +9261,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -9479,10 +9506,10 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -9560,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -9586,7 +9613,7 @@
         <v>7</v>
       </c>
       <c r="I5" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -9719,7 +9746,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -9823,7 +9850,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -9849,7 +9876,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -9982,7 +10009,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -10086,7 +10113,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -10112,7 +10139,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -10245,7 +10272,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -10349,7 +10376,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -10375,7 +10402,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -10401,7 +10428,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -10534,7 +10561,7 @@
         <v>7</v>
       </c>
       <c r="J41" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -10785,10 +10812,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -10875,7 +10902,7 @@
         <v>287</v>
       </c>
       <c r="I4" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -11020,7 +11047,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -11165,7 +11192,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -11342,7 +11369,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -11455,7 +11482,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -11484,7 +11511,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -11513,7 +11540,7 @@
         <v>7</v>
       </c>
       <c r="I26" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -11661,7 +11688,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -11777,7 +11804,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -11806,7 +11833,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -11954,7 +11981,7 @@
         <v>7</v>
       </c>
       <c r="J41" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -12106,10 +12133,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -12196,7 +12223,7 @@
         <v>343</v>
       </c>
       <c r="I4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -12225,7 +12252,7 @@
         <v>346</v>
       </c>
       <c r="I5" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -12373,7 +12400,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -12489,7 +12516,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -12518,7 +12545,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -12666,7 +12693,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -12782,7 +12809,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -12811,7 +12838,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -12959,7 +12986,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -13075,7 +13102,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -13104,7 +13131,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -13133,7 +13160,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -13281,7 +13308,7 @@
         <v>7</v>
       </c>
       <c r="J41" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -13412,10 +13439,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -13502,7 +13529,7 @@
         <v>401</v>
       </c>
       <c r="I4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -13531,7 +13558,7 @@
         <v>404</v>
       </c>
       <c r="I5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -13679,7 +13706,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -13795,7 +13822,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -13824,7 +13851,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -13972,7 +13999,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -14088,7 +14115,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -14117,7 +14144,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -14146,7 +14173,7 @@
         <v>7</v>
       </c>
       <c r="I26" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -14175,7 +14202,7 @@
         <v>7</v>
       </c>
       <c r="I27" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -14323,7 +14350,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -14439,7 +14466,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -14468,7 +14495,7 @@
         <v>7</v>
       </c>
       <c r="I37" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -14616,7 +14643,7 @@
         <v>7</v>
       </c>
       <c r="J42" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -14746,10 +14773,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -14836,7 +14863,7 @@
         <v>327</v>
       </c>
       <c r="I4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -14984,7 +15011,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -15088,7 +15115,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -15111,7 +15138,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -15229,7 +15256,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -15333,7 +15360,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -15362,7 +15389,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -15510,7 +15537,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -15626,7 +15653,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -15655,7 +15682,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -15684,7 +15711,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -15832,7 +15859,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -15975,10 +16002,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -16041,7 +16068,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -16144,7 +16171,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -16227,7 +16254,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -16330,7 +16357,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -16413,7 +16440,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -16436,7 +16463,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -16539,7 +16566,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -16622,7 +16649,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -16645,7 +16672,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -16748,7 +16775,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -16852,10 +16879,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>748</v>
+      </c>
+      <c r="J1" t="s">
         <v>749</v>
-      </c>
-      <c r="J1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -16942,7 +16969,7 @@
         <v>556</v>
       </c>
       <c r="I4" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -16971,7 +16998,7 @@
         <v>559</v>
       </c>
       <c r="I5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -17116,7 +17143,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -17232,7 +17259,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -17261,7 +17288,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -17409,7 +17436,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -17525,7 +17552,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -17554,7 +17581,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -17583,7 +17610,7 @@
         <v>7</v>
       </c>
       <c r="I26" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -17702,7 +17729,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -17847,7 +17874,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -17995,7 +18022,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">

--- a/src/main/java/video/call/data/answers.xlsx
+++ b/src/main/java/video/call/data/answers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gen.data.test\src\main\java\video\call\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DD4D9A-4C03-4281-A708-E5D0756A470F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEF7D53-C044-4E4D-8BBB-810A6E0A6C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="My new backpack!" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4566" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4562" uniqueCount="877">
   <si>
     <t>Part</t>
   </si>
@@ -2350,9 +2350,6 @@
     <t>green</t>
   </si>
   <si>
-    <t>Yes/ Yes, I want corn</t>
-  </si>
-  <si>
     <t>Yes/ Yeah/ Yep</t>
   </si>
   <si>
@@ -2368,12 +2365,6 @@
     <t>awesome/ great/ not too bad</t>
   </si>
   <si>
-    <t>snowball fight</t>
-  </si>
-  <si>
-    <t>gang violence</t>
-  </si>
-  <si>
     <t>grapes/ oranges/ pineapples</t>
   </si>
   <si>
@@ -2473,9 +2464,6 @@
     <t>no/ No, I'm not thirsty./ I'm okay</t>
   </si>
   <si>
-    <t>Yes/ Yes,thanks/ milk/ Yes, please</t>
-  </si>
-  <si>
     <t>No/ Milk is bad</t>
   </si>
   <si>
@@ -2521,15 +2509,6 @@
     <t>one/ hand</t>
   </si>
   <si>
-    <t>thanks/ please/ bad</t>
-  </si>
-  <si>
-    <t>juice/ coke</t>
-  </si>
-  <si>
-    <t>wine/ beer/ alcohol/ drug</t>
-  </si>
-  <si>
     <t>no/ ran</t>
   </si>
   <si>
@@ -2542,9 +2521,6 @@
     <t>No/ No, I don't want corn</t>
   </si>
   <si>
-    <t>corn/ want/ i</t>
-  </si>
-  <si>
     <t>Beansprouts/ Bamboo Shoot</t>
   </si>
   <si>
@@ -2572,9 +2548,6 @@
     <t>camping/ swimming</t>
   </si>
   <si>
-    <t>violence/ fight</t>
-  </si>
-  <si>
     <t>sound/ r</t>
   </si>
   <si>
@@ -2666,6 +2639,30 @@
   </si>
   <si>
     <t>2_13</t>
+  </si>
+  <si>
+    <t>thanks/ bad</t>
+  </si>
+  <si>
+    <t>Yes/ Yes,thanks/ milk/ Yes, please/ please</t>
+  </si>
+  <si>
+    <t>juice</t>
+  </si>
+  <si>
+    <t>wine/ beer/ alcohol/ drug/ coke</t>
+  </si>
+  <si>
+    <t>corn/ i</t>
+  </si>
+  <si>
+    <t>Yes/ Yes, I want corn/ want</t>
+  </si>
+  <si>
+    <t>gang violence/ violence/ fight</t>
+  </si>
+  <si>
+    <t>skiing</t>
   </si>
 </sst>
 </file>
@@ -3386,7 +3383,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -3650,7 +3647,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -3766,7 +3763,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -3795,7 +3792,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -3943,7 +3940,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -4059,7 +4056,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -4207,7 +4204,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -4273,7 +4270,7 @@
         <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C40" t="s">
         <v>139</v>
@@ -4323,7 +4320,7 @@
         <v>7</v>
       </c>
       <c r="I41" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -4693,7 +4690,7 @@
         <v>607</v>
       </c>
       <c r="I4" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4841,7 +4838,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -4957,7 +4954,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -5105,7 +5102,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -5221,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -5250,7 +5247,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -5398,7 +5395,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -5514,7 +5511,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -5543,7 +5540,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -5572,7 +5569,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -5601,7 +5598,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -5746,7 +5743,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -5889,7 +5886,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>10</v>
@@ -5959,7 +5956,7 @@
         <v>659</v>
       </c>
       <c r="I4" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5988,7 +5985,7 @@
         <v>662</v>
       </c>
       <c r="I5" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6017,7 +6014,7 @@
         <v>664</v>
       </c>
       <c r="I6" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6046,7 +6043,7 @@
         <v>665</v>
       </c>
       <c r="I7" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6178,12 +6175,12 @@
         <v>7</v>
       </c>
       <c r="J12" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>48</v>
@@ -6210,7 +6207,7 @@
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>52</v>
@@ -6284,7 +6281,7 @@
         <v>7</v>
       </c>
       <c r="I16" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6313,7 +6310,7 @@
         <v>7</v>
       </c>
       <c r="I17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6342,7 +6339,7 @@
         <v>7</v>
       </c>
       <c r="I18" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6371,7 +6368,7 @@
         <v>7</v>
       </c>
       <c r="I19" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6536,12 +6533,12 @@
         <v>7</v>
       </c>
       <c r="J25" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>48</v>
@@ -6568,7 +6565,7 @@
     </row>
     <row r="27" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>52</v>
@@ -6642,7 +6639,7 @@
         <v>7</v>
       </c>
       <c r="I29" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6671,7 +6668,7 @@
         <v>7</v>
       </c>
       <c r="I30" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7019,7 +7016,7 @@
         <v>707</v>
       </c>
       <c r="I4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -7167,7 +7164,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -7280,7 +7277,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -7428,7 +7425,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -7544,7 +7541,7 @@
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -7692,7 +7689,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -7808,7 +7805,7 @@
         <v>7</v>
       </c>
       <c r="I31" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -7837,7 +7834,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -8380,7 +8377,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -8496,7 +8493,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -8525,7 +8522,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -8554,7 +8551,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -8690,7 +8687,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -8968,7 +8965,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -9084,7 +9081,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -9113,7 +9110,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -9261,7 +9258,7 @@
         <v>7</v>
       </c>
       <c r="J40" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -9587,7 +9584,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -9613,7 +9610,7 @@
         <v>7</v>
       </c>
       <c r="I5" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -9746,7 +9743,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -9850,7 +9847,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>813</v>
+        <v>870</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -9876,7 +9873,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -10009,7 +10006,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>829</v>
+        <v>869</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -10113,7 +10110,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -10139,7 +10136,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -10272,7 +10269,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -10376,7 +10373,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>830</v>
+        <v>871</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -10402,7 +10399,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>831</v>
+        <v>872</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -11688,7 +11685,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -12223,7 +12220,7 @@
         <v>343</v>
       </c>
       <c r="I4" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -12516,7 +12513,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>772</v>
+        <v>874</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -12545,7 +12542,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -12693,7 +12690,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>836</v>
+        <v>873</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -12809,7 +12806,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -13102,7 +13099,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -13131,7 +13128,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -13153,14 +13150,11 @@
       <c r="F36" t="s">
         <v>7</v>
       </c>
-      <c r="G36" t="s">
-        <v>7</v>
-      </c>
       <c r="H36" t="s">
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -13308,7 +13302,7 @@
         <v>7</v>
       </c>
       <c r="J41" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -13529,7 +13523,7 @@
         <v>401</v>
       </c>
       <c r="I4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -13558,7 +13552,7 @@
         <v>404</v>
       </c>
       <c r="I5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -13706,7 +13700,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -13822,7 +13816,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -13847,11 +13841,8 @@
       <c r="G15" t="s">
         <v>7</v>
       </c>
-      <c r="H15" t="s">
-        <v>7</v>
-      </c>
       <c r="I15" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -13999,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -14115,7 +14106,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -14144,7 +14135,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>778</v>
+        <v>876</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -14192,9 +14183,6 @@
       <c r="E27" t="s">
         <v>21</v>
       </c>
-      <c r="F27" t="s">
-        <v>7</v>
-      </c>
       <c r="G27" t="s">
         <v>7</v>
       </c>
@@ -14202,7 +14190,7 @@
         <v>7</v>
       </c>
       <c r="I27" t="s">
-        <v>779</v>
+        <v>875</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -14349,9 +14337,6 @@
       <c r="I32" t="s">
         <v>7</v>
       </c>
-      <c r="J32" t="s">
-        <v>846</v>
-      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -14466,7 +14451,7 @@
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -14495,7 +14480,7 @@
         <v>7</v>
       </c>
       <c r="I37" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -14643,7 +14628,7 @@
         <v>7</v>
       </c>
       <c r="J42" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -14863,7 +14848,7 @@
         <v>327</v>
       </c>
       <c r="I4" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -15115,7 +15100,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -15138,7 +15123,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -15256,7 +15241,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -15360,7 +15345,7 @@
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -15653,7 +15638,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -15682,7 +15667,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -15711,7 +15696,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -16068,7 +16053,7 @@
         <v>7</v>
       </c>
       <c r="I4" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -16171,7 +16156,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -16254,7 +16239,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -16649,7 +16634,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -16672,7 +16657,7 @@
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -16969,7 +16954,7 @@
         <v>556</v>
       </c>
       <c r="I4" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -16998,7 +16983,7 @@
         <v>559</v>
       </c>
       <c r="I5" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -17259,7 +17244,7 @@
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -17288,7 +17273,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -17552,7 +17537,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -17581,7 +17566,7 @@
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -17729,7 +17714,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -17874,7 +17859,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
